--- a/sample.xlsx
+++ b/sample.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>안녕하세요 테스트 메세지입니다.</t>
+          <t>지금 바로 만나보세요. 고객 만족도가 높은 프리미엄 서비스로 일상에 특별한 변화를 더해드립니다. 합리적인 가격과 뛰어난 품질, 빠른 상담과 친절한 지원까지 한 번에 경험할 수 있습니다. 한정 기간 특별 할인 혜택과 신규 고객 전용 이벤트도 함께 진행 중이니 놓치지 마세요. 지금 신청하시면 추가 혜택과 사은품까지 제공되며, 많은 고객이 선택한 이유를 직접 확인하실 수 있습니다. 믿을 수 있는 서비스, 검증된 품질, 만족도 높은 결과로 여러분의 기대를 넘어서는 경험을 약속드립니다. 지금 바로 문의하시고 특별한 혜택을 받아보세요.</t>
         </is>
       </c>
       <c r="C2" s="0" t="n">
@@ -495,7 +495,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>임상민님 두번째 테스트입니다.</t>
+          <t>지금 바로 만나보세요. 고객 만족도가 높은 프리미엄 서비스로 일상에 특별한 변화를 더해드립니다. 합리적인 가격과 뛰어난 품질, 빠른 상담과 친절한 지원까지 한 번에 경험할 수 있습니다. 한정 기간 특별 할인 혜택과 신규 고객 전용 이벤트도 함께 진행 중이니 놓치지 마세요. 지금 신청하시면 추가 혜택과 사은품까지 제공되며, 많은 고객이 선택한 이유를 직접 확인하실 수 있습니다. 믿을 수 있는 서비스, 검증된 품질, 만족도 높은 결과로 여러분의 기대를 넘어서는 경험을 약속드립니다. 지금 바로 문의하시고 특별한 혜택을 받아보세요.</t>
         </is>
       </c>
       <c r="C3" s="0" t="n">
@@ -509,5 +509,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" copies="50"/>
 </worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4395" yWindow="1920" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,10 +28,10 @@
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -59,25 +59,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -452,63 +453,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="9" customWidth="1" style="2" min="1" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" s="3">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>A(target)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>B(message)</t>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>to_email</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>detail</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="66" customHeight="1" s="3">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>다솜이</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>지금 바로 만나보세요. 고객 만족도가 높은 프리미엄 서비스로 일상에 특별한 변화를 더해드립니다. 합리적인 가격과 뛰어난 품질, 빠른 상담과 친절한 지원까지 한 번에 경험할 수 있습니다. 한정 기간 특별 할인 혜택과 신규 고객 전용 이벤트도 함께 진행 중이니 놓치지 마세요. 지금 신청하시면 추가 혜택과 사은품까지 제공되며, 많은 고객이 선택한 이유를 직접 확인하실 수 있습니다. 믿을 수 있는 서비스, 검증된 품질, 만족도 높은 결과로 여러분의 기대를 넘어서는 경험을 약속드립니다. 지금 바로 문의하시고 특별한 혜택을 받아보세요.</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>클립보드 붙여넣기 후 엔터 전송 완료</t>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="66" customHeight="1" s="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>임상민</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>지금 바로 만나보세요. 고객 만족도가 높은 프리미엄 서비스로 일상에 특별한 변화를 더해드립니다. 합리적인 가격과 뛰어난 품질, 빠른 상담과 친절한 지원까지 한 번에 경험할 수 있습니다. 한정 기간 특별 할인 혜택과 신규 고객 전용 이벤트도 함께 진행 중이니 놓치지 마세요. 지금 신청하시면 추가 혜택과 사은품까지 제공되며, 많은 고객이 선택한 이유를 직접 확인하실 수 있습니다. 믿을 수 있는 서비스, 검증된 품질, 만족도 높은 결과로 여러분의 기대를 넘어서는 경험을 약속드립니다. 지금 바로 문의하시고 특별한 혜택을 받아보세요.</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>테스트입니다</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>colaa123@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>테스트메일</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>이메일 테스트</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" copies="50"/>
 </worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="870" yWindow="1890" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -453,10 +453,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="9" customWidth="1" style="2" min="1" max="6"/>
+    <col width="9" customWidth="1" style="2" min="1" max="2"/>
+    <col width="22.125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.25" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14.75" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9" customWidth="1" style="2" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,6 +573,106 @@
       </c>
       <c r="F4" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>승찬</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>이정찬</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>허준범</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>영재</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -576,5 +680,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" copies="50"/>
 </worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -576,100 +576,100 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>kakao</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>승찬</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>안녕하세요</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>kakao</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>이정찬</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>안녕하세요</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>kakao</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>허준범</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>안녕하세요</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>kakao</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>영재</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>안녕하세요</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
         </is>

--- a/sample.xlsx
+++ b/sample.xlsx
@@ -1,50 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\hjss_p\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBB51F0-E49E-4512-AEB4-8AF79D145449}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="870" yWindow="1890" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>to_email</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>detail</t>
+  </si>
+  <si>
+    <t>kakao</t>
+  </si>
+  <si>
+    <t>다솜이</t>
+  </si>
+  <si>
+    <t>안녕하세요</t>
+  </si>
+  <si>
+    <t>임상민</t>
+  </si>
+  <si>
+    <t>테스트입니다</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>colaa123@naver.com</t>
+  </si>
+  <si>
+    <t>이메일 주 제목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일 내용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -60,95 +120,36 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -448,238 +449,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="9" customWidth="1" style="2" min="1" max="2"/>
-    <col width="22.125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="13.25" customWidth="1" style="2" min="4" max="4"/>
-    <col width="14.75" customWidth="1" style="2" min="5" max="5"/>
-    <col width="9" customWidth="1" style="2" min="6" max="6"/>
+    <col min="1" max="2" width="9" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>to_email</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>subject</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>다솜이</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>안녕하세요</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>임상민</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>테스트입니다</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>colaa123@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>테스트메일</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>이메일 테스트</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>승찬</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>안녕하세요</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>이정찬</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>안녕하세요</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>허준범</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>안녕하세요</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>kakao</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>영재</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>안녕하세요</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
-        </is>
-      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" copies="50"/>
+  <pageSetup paperSize="9" orientation="landscape" copies="50" r:id="rId2"/>
 </worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -1,110 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\hjss_p\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBB51F0-E49E-4512-AEB4-8AF79D145449}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>channel</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>to_email</t>
-  </si>
-  <si>
-    <t>subject</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>detail</t>
-  </si>
-  <si>
-    <t>kakao</t>
-  </si>
-  <si>
-    <t>다솜이</t>
-  </si>
-  <si>
-    <t>안녕하세요</t>
-  </si>
-  <si>
-    <t>임상민</t>
-  </si>
-  <si>
-    <t>테스트입니다</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>colaa123@naver.com</t>
-  </si>
-  <si>
-    <t>이메일 주 제목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이메일 내용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,36 +60,95 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,141 +448,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2" customWidth="1"/>
+    <col width="9" customWidth="1" style="2" min="1" max="2"/>
+    <col width="22.125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.25" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14.75" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9" customWidth="1" style="2" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>to_email</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>다솜이</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>임상민</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>테스트입니다</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>send_chat_text: 클립보드 붙여넣기 후 엔터 전송 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>colaa123@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>이메일 주 제목</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>이메일 내용</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n"/>
+      <c r="B5" s="0" t="n"/>
+      <c r="C5" s="0" t="n"/>
+      <c r="D5" s="0" t="n"/>
+      <c r="E5" s="0" t="n"/>
+      <c r="F5" s="0" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="n"/>
+      <c r="D6" s="0" t="n"/>
+      <c r="E6" s="0" t="n"/>
+      <c r="F6" s="0" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n"/>
+      <c r="B7" s="0" t="n"/>
+      <c r="C7" s="0" t="n"/>
+      <c r="D7" s="0" t="n"/>
+      <c r="E7" s="0" t="n"/>
+      <c r="F7" s="0" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n"/>
+      <c r="B8" s="0" t="n"/>
+      <c r="C8" s="0" t="n"/>
+      <c r="D8" s="0" t="n"/>
+      <c r="E8" s="0" t="n"/>
+      <c r="F8" s="0" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n"/>
+      <c r="B9" s="0" t="n"/>
+      <c r="C9" s="0" t="n"/>
+      <c r="D9" s="0" t="n"/>
+      <c r="E9" s="0" t="n"/>
+      <c r="F9" s="0" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n"/>
+      <c r="B10" s="0" t="n"/>
+      <c r="C10" s="0" t="n"/>
+      <c r="D10" s="0" t="n"/>
+      <c r="E10" s="0" t="n"/>
+      <c r="F10" s="0" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="n"/>
+      <c r="C11" s="0" t="n"/>
+      <c r="D11" s="0" t="n"/>
+      <c r="E11" s="0" t="n"/>
+      <c r="F11" s="0" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" copies="50" r:id="rId2"/>
+  <pageSetup orientation="landscape" paperSize="9" copies="50"/>
 </worksheet>
 </file>